--- a/src-tauri/samples/mame/07_mame_activity_long.xlsx
+++ b/src-tauri/samples/mame/07_mame_activity_long.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_long" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="activity" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.011</v>
+        <v>0.47</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -464,14 +464,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.962</v>
+        <v>0.44</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -482,14 +482,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.982</v>
+        <v>0.51</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -500,11 +500,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.828</v>
+        <v>1.51</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -518,14 +518,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.869</v>
+        <v>1.53</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -536,14 +536,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.864</v>
+        <v>1.56</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -554,11 +554,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.511</v>
+        <v>0.88</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -572,14 +572,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.447</v>
+        <v>0.91</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -590,14 +590,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.474</v>
+        <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -608,11 +608,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.292</v>
+        <v>1.05</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -626,14 +626,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.307</v>
+        <v>1.02</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -644,14 +644,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B6</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.33</v>
+        <v>1.09</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -662,11 +662,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.512</v>
+        <v>1.84</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -680,14 +680,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.526</v>
+        <v>1.87</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -698,14 +698,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.562</v>
+        <v>1.86</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -716,11 +716,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.204</v>
+        <v>1.63</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -734,14 +734,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.178</v>
+        <v>1.6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -752,14 +752,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.207</v>
+        <v>1.66</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -770,11 +770,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.135</v>
+        <v>3.11</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -788,14 +788,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.071</v>
+        <v>3.07</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -806,14 +806,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.134</v>
+        <v>3.13</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -824,14 +824,212 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.026</v>
+        <v>2.29</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>WT_1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>WT_2</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>WT_3</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src-tauri/samples/mame/07_mame_activity_long.xlsx
+++ b/src-tauri/samples/mame/07_mame_activity_long.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.47</v>
+        <v>2.41</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.44</v>
+        <v>2.38</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.51</v>
+        <v>2.44</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.88</v>
+        <v>3.12</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.91</v>
+        <v>3.07</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.86</v>
+        <v>3.15</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.09</v>
+        <v>0.66</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.11</v>
+        <v>0.88</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.07</v>
+        <v>0.85</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.13</v>
+        <v>0.91</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.31</v>
+        <v>1.3</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.33</v>
+        <v>1.36</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.34</v>
+        <v>0.47</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.31</v>
+        <v>0.44</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.37</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>

--- a/src-tauri/samples/mame/07_mame_activity_long.xlsx
+++ b/src-tauri/samples/mame/07_mame_activity_long.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,11 +986,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WT_1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1004,11 +1004,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WT_2</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
@@ -1022,13 +1022,337 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>WT_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>WT_2</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>plate01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>WT_3</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
         <v>3</v>
       </c>
     </row>
